--- a/out/LSTM-Mamba1_repeat_4_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>-6.75351114863297e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>0.7785800168151985</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>1.558363729382479</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0.1167515465921939</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>1.012241738182021</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0.1459774784774187</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>1.18746364413097</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0.209257860438623</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>1.460084593687064</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0.2238644609173098</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>1.698571628299907</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0.237251944347076</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>1.949227299831098</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0.1070667240257002</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>1.925912980847788</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0.05170897721724928</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>1.922178923545358</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0.02463717527422079</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>1.919704459501471</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0.007297419349351257</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>1.909637419604475</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0.004825271689484421</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>1.911987494252265</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0.002466695254996821</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>1.912093724905556</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0.001259367644650069</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>1.912144317334213</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0.0004703237279909154</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>1.911824389174857</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0.0002540518768592011</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>1.911861972613917</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0.0001197726022376576</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>1.911847271824636</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>7.273245427736819e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>1.911872110684413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>3.514539714193261e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>1.911870653856644</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>1.498186261570356e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>1.911864417038152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>7.791463777627117e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>1.911865009306555</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>1.911858865510579</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>1.911853180976551</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>1.911848429701337</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>1.911843140553775</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>1.911843117819474</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>1.91184343609969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>1.911844527346148</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>1.911843837739012</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>1.911843868051413</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>1.911843678598903</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>1.911843731645606</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>1.911843784692309</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>1.9118436179741</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>1.911843367896787</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>1.911843132975675</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>1.911843375474887</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>1.911843572505498</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>1.911843549771197</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>1.91184342094349</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>1.91184342852159</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>1.911843693755104</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>1.911843640708401</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>1.911843724067505</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>1.911843557349297</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>1.911843193600478</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>1.911843087507072</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>1.911843148131875</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>1.911843019304169</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>1.911843155709976</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>1.911843011726068</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>1.911843026882269</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>1.911843254225281</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>1.91184323906908</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>1.911843345162486</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>1.911843072350872</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>1.911843170866177</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>1.911843284537683</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>1.911843269381482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>0</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.857095742388521e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002160652540624142</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001611510291695595</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001295356778427958</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.00111096678301692</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0009625214152038097</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0008587872143834829</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.000788563396781683</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0007320072036236525</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0006858394481241703</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0006518762093037367</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0006210131105035543</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0005953104700893164</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0005720953922718763</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0005586917977780104</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.000535756116732955</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0004993958864361048</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0004597713705152273</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0004296281840652227</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0003948092926293612</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0003636716865003109</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0003579757176339626</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0003842012956738472</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0004383139312267303</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0004817275330424309</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0005112227518111467</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0005306648090481758</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0005394946783781052</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.000545549439266324</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.000577293336391449</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0005978960543870926</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0006183013319969177</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0006265444681048393</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0006209257990121841</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0006169741973280907</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0006266080308705568</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0006699066143482924</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0007701225113123655</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0008888407610356808</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.001000149641185999</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>0</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.001080467831343412</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>0</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001145883114077151</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>0</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.001227369415573776</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.001360982074402273</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.00158340111374855</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001796442200429738</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001973985228687525</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.002054797252640128</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.002041299361735582</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.002035139361396432</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.00202502915635705</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002006600610911846</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001968503464013338</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001943411072716117</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001929934369400144</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.001948738005012274</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.00197552889585495</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002003378234803677</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.00207543233409524</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002126897452399135</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00214309711009264</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.002142660552635789</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002109250985085964</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002087058499455452</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002131490269675851</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002280534710735083</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002408969448879361</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002499810419976711</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002545400988310575</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002570893615484238</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.002582212910056114</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002573862206190825</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002536742482334375</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002469415776431561</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002387884305790067</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.002325437497347593</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002271952573210001</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002226971322670579</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002175952540710568</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002170030493289232</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.00218673818744719</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002192454179748893</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002205472439527512</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002234836108982563</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002263260539621115</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002266922267153859</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.00225544604472816</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.002252526115626097</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.002258164109662175</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.002285798313096166</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002295827958732843</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002329590730369091</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002370422706007957</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.002385438652709126</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002407258376479149</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0023760418407619</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.002312975004315376</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002257660496979952</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002208915306255221</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002140623051673174</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.002086801687255502</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00203652260825038</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002030167961493134</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002068239729851484</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002118152566254139</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002144291298463941</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002137519419193268</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00208007637411356</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002034238306805491</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002029660623520613</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.00204735342413187</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002072650473564863</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002056480385363102</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002051126211881638</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002072994597256184</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002100839279592037</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002126609208062291</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002156092552468181</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002188963815569878</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002195149194449186</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002184593817219138</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002164927311241627</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002147020306438208</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002136114053428173</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002135213930159807</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00213457946665585</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.002160652540624142</v>
+        <v>-0.002160651609301567</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.44</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.00111096678301692</v>
+        <v>-0.001110967248678207</v>
       </c>
       <c r="JB5" t="n">
         <v>0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0009625214152038097</v>
+        <v>-0.0009625216480344534</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0008587872143834829</v>
+        <v>-0.0008587874472141266</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.000788563396781683</v>
+        <v>-0.0007885640952736139</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0007320072036236525</v>
+        <v>-0.0007320076692849398</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0006858394481241703</v>
+        <v>-0.0006858406122773886</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0006518762093037367</v>
+        <v>-0.0006518724840134382</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0006210131105035543</v>
+        <v>-0.0006210128776729107</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0005953104700893164</v>
+        <v>-0.0005953093059360981</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0005720953922718763</v>
+        <v>-0.0005720942281186581</v>
       </c>
       <c r="JB14" t="n">
         <v>0.3999999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0005586917977780104</v>
+        <v>-0.0005586864426732063</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3999999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.000535756116732955</v>
+        <v>-0.0005357544869184494</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0004597713705152273</v>
+        <v>-0.0004597676452249289</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0004296281840652227</v>
+        <v>-0.0004296263214200735</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0003948092926293612</v>
+        <v>-0.00039480603300035</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.0003636716865003109</v>
+        <v>-0.0003636705223470926</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0003579757176339626</v>
+        <v>-0.0003579750191420317</v>
       </c>
       <c r="JB22" t="n">
         <v>0.2599999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.0003842012956738472</v>
+        <v>-0.0003842008300125599</v>
       </c>
       <c r="JB23" t="n">
         <v>0.1199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0004383139312267303</v>
+        <v>-0.000438314164057374</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.02000000000000007</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0004817275330424309</v>
+        <v>-0.0004817235749214888</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.0005112227518111467</v>
+        <v>-0.0005112208891659975</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0005306648090481758</v>
+        <v>-0.0005306645762175322</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0005394946783781052</v>
+        <v>-0.0005394942127168179</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.000545549439266324</v>
+        <v>-0.0005455487407743931</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.000577293336391449</v>
+        <v>-0.0005772921722382307</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0005978960543870926</v>
+        <v>-0.0005978953558951616</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0006183013319969177</v>
+        <v>-0.0006183020304888487</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0006265444681048393</v>
+        <v>-0.0006265421397984028</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0006209257990121841</v>
+        <v>-0.0006209248676896095</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0006169741973280907</v>
+        <v>-0.0006169751286506653</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0006266080308705568</v>
+        <v>-0.0006266094278544188</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0006699066143482924</v>
+        <v>-0.0006699082441627979</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0007701225113123655</v>
+        <v>-0.0007701234426349401</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0008888407610356808</v>
+        <v>-0.0008888414595276117</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.001000149641185999</v>
+        <v>-0.001000150805339217</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001145883114077151</v>
+        <v>-0.00114588369615376</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.001227369415573776</v>
+        <v>-0.001227368251420557</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.001360982074402273</v>
+        <v>-0.001360981725156307</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.00158340111374855</v>
+        <v>-0.001583396922796965</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001796442200429738</v>
+        <v>-0.001796437310986221</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001973985228687525</v>
+        <v>-0.001973989419639111</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.002054797252640128</v>
+        <v>-0.002054798882454634</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.002041299361735582</v>
+        <v>-0.002041300293058157</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.002035139361396432</v>
+        <v>-0.00203514052554965</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.002006600610911846</v>
+        <v>-0.002006602939218283</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.001968503464013338</v>
+        <v>-0.001968502998352051</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.001929934369400144</v>
+        <v>-0.001929940422996879</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.001948738005012274</v>
+        <v>-0.001948744524270296</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.00197552889585495</v>
+        <v>-0.001975531224161386</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.002003378234803677</v>
+        <v>-0.002003381494432688</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.00207543233409524</v>
+        <v>-0.002075436990708113</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.002126897452399135</v>
+        <v>-0.002126901876181364</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.00214309711009264</v>
+        <v>-0.002143102930858731</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.002142660552635789</v>
+        <v>-0.002142667537555099</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.002109250985085964</v>
+        <v>-0.002109259366989136</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002087058499455452</v>
+        <v>-0.002087064553052187</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002280534710735083</v>
+        <v>-0.002280542626976967</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002408969448879361</v>
+        <v>-0.00240896875038743</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002499810419976711</v>
+        <v>-0.002499799244105816</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.002545400988310575</v>
+        <v>-0.002545395167544484</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002570893615484238</v>
+        <v>-0.002570890821516514</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.002582212910056114</v>
+        <v>-0.002582216402515769</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002573862206190825</v>
+        <v>-0.002573867794126272</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.002536742482334375</v>
+        <v>-0.002536772051826119</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002469415776431561</v>
+        <v>-0.002469429280608892</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002387884305790067</v>
+        <v>-0.002387895015999675</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.002325437497347593</v>
+        <v>-0.002325444016605616</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.2599999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.002271952573210001</v>
+        <v>-0.002271960023790598</v>
       </c>
       <c r="JB77" t="n">
         <v>0.02000000000000007</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002226971322670579</v>
+        <v>-0.002226980635896325</v>
       </c>
       <c r="JB78" t="n">
         <v>0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002175952540710568</v>
+        <v>-0.002175955567508936</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.002170030493289232</v>
+        <v>-0.002170035382732749</v>
       </c>
       <c r="JB80" t="n">
         <v>0.8599999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.00218673818744719</v>
+        <v>-0.002186739817261696</v>
       </c>
       <c r="JB81" t="n">
         <v>0.8599999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002192454179748893</v>
+        <v>-0.00219245906919241</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002205472439527512</v>
+        <v>-0.002205474069342017</v>
       </c>
       <c r="JB83" t="n">
         <v>0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002234836108982563</v>
+        <v>-0.002234838670119643</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.002263260539621115</v>
+        <v>-0.002263261936604977</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002266922267153859</v>
+        <v>-0.002266921801492572</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.00225544604472816</v>
+        <v>-0.002255448838695884</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.002252526115626097</v>
+        <v>-0.00225252634845674</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.002258164109662175</v>
+        <v>-0.002258164808154106</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.002285798313096166</v>
+        <v>-0.002285802969709039</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002295827958732843</v>
+        <v>-0.002295834710821509</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.002329590730369091</v>
+        <v>-0.002329594688490033</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.002370422706007957</v>
+        <v>-0.002370424102991819</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.002385438652709126</v>
+        <v>-0.002385439351201057</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.002407258376479149</v>
+        <v>-0.002407263498753309</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.0023760418407619</v>
+        <v>-0.002376046264544129</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.002312975004315376</v>
+        <v>-0.002312980825081468</v>
       </c>
       <c r="JB97" t="n">
         <v>0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.002257660496979952</v>
+        <v>-0.002257663290947676</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.002208915306255221</v>
+        <v>-0.002208923455327749</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.002140623051673174</v>
+        <v>-0.002140626776963472</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.002086801687255502</v>
+        <v>-0.002086801920086145</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.00203652260825038</v>
+        <v>-0.002036526799201965</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.002030167961493134</v>
+        <v>-0.002030170522630215</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002068239729851484</v>
+        <v>-0.002068246249109507</v>
       </c>
       <c r="JB104" t="n">
         <v>0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.002118152566254139</v>
+        <v>-0.002118155593052506</v>
       </c>
       <c r="JB105" t="n">
         <v>0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.002144291298463941</v>
+        <v>-0.002144294790923595</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.02000000000000007</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.002137519419193268</v>
+        <v>-0.002137526869773865</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.02000000000000007</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.00208007637411356</v>
+        <v>-0.002080083126202226</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.02000000000000007</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002034238306805491</v>
+        <v>-0.002034241333603859</v>
       </c>
       <c r="JB109" t="n">
         <v>0.1199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002029660623520613</v>
+        <v>-0.00202966621145606</v>
       </c>
       <c r="JB110" t="n">
         <v>0.2599999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.00204735342413187</v>
+        <v>-0.002047359244897962</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.002072650473564863</v>
+        <v>-0.002072652336210012</v>
       </c>
       <c r="JB112" t="n">
         <v>0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002056480385363102</v>
+        <v>-0.002056481782346964</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002051126211881638</v>
+        <v>-0.002051130868494511</v>
       </c>
       <c r="JB114" t="n">
         <v>0.5799999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002072994597256184</v>
+        <v>-0.002072999952360988</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002100839279592037</v>
+        <v>-0.002100840210914612</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.3</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002126609208062291</v>
+        <v>-0.0021266033872962</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002156092552468181</v>
+        <v>-0.002156089525669813</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.002188963815569878</v>
+        <v>-0.002188960555940866</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002195149194449186</v>
+        <v>-0.002195146633312106</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.002184593817219138</v>
+        <v>-0.00218459265306592</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002164927311241627</v>
+        <v>-0.002164932200685143</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.002147020306438208</v>
+        <v>-0.002147022169083357</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002136114053428173</v>
+        <v>-0.002136114751920104</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002135213930159807</v>
+        <v>-0.00213521858677268</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.00213457946665585</v>
+        <v>-0.002134582493454218</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3</v>
